--- a/BASE_EXCEL_TEMPLATES/la_kh_land/LA_KH_LAND_2026_V00_SHIPMENTS.xlsx
+++ b/BASE_EXCEL_TEMPLATES/la_kh_land/LA_KH_LAND_2026_V00_SHIPMENTS.xlsx
@@ -5,22 +5,22 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ssapd\StudioProjects\백업 및 추가 자료 보관\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ssapd\StudioProjects\lkgroup_app\base\la_kh_land\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A41E546-99E9-4CCE-B363-D410F2FB91A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D37609A-05DA-457D-B626-81BB3CE96C8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="908" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="45" yWindow="0" windowWidth="17775" windowHeight="13770" tabRatio="908" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Row data" sheetId="3" r:id="rId1"/>
     <sheet name="수취인 불명 내역" sheetId="1592" state="hidden" r:id="rId2"/>
-    <sheet name="이름(LCBLxx-xx)" sheetId="1534" r:id="rId3"/>
+    <sheet name="이름(LCBxx-xx)" sheetId="1534" r:id="rId3"/>
     <sheet name="Sheet1" sheetId="1593" r:id="rId4"/>
     <sheet name="Sheet2" sheetId="1594" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'이름(LCBLxx-xx)'!$A$1:$N$28</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'이름(LCBxx-xx)'!$A$1:$N$28</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -511,14 +511,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Lao-Cambodia-Lao Trucking 거래 명세서</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>LKLCBL 2026xx-xx</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>경남은행 2070133424601 박성호(엘케이무역)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -528,10 +520,6 @@
   </si>
   <si>
     <t>경남은행 571-22-0330221 박성호</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>LCBL10-01</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -561,6 +549,18 @@
   <si>
     <t>- valid end of Aug/2026, after confirm price but incase departrue delayed by customer request or needs, rate should be change.
 - 기한: 2026년 08월 말, 고객의 요청에 의하여 견적후 배송/출발 지연이 발생할 경우 운임 변동이 있을수 있으니 참고 부탁 드립니다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lao-Cambodia Trucking 거래 명세서</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>LKLCB 2026xx-xx</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>LCB10-01</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1455,43 +1455,76 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="3" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="6" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="13" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="11" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="14" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="27" fillId="9" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1524,76 +1557,43 @@
     <xf numFmtId="0" fontId="28" fillId="9" borderId="12" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="3" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="6" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="13" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="11" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="14" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2277,7 +2277,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="$A$1:$N$28" spid="_x0000_s1127"/>
+                  <a14:cameraTool cellRange="$A$1:$N$28" spid="_x0000_s1128"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -2704,7 +2704,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="36" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B8" s="36">
         <v>0</v>
@@ -2718,7 +2718,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="36" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B9" s="36">
         <v>2</v>
@@ -2732,7 +2732,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="36" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B10" s="36">
         <v>3</v>
@@ -2746,7 +2746,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="36" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B11" s="36">
         <v>4</v>
@@ -2788,7 +2788,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="36" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B14" s="36">
         <v>15</v>
@@ -2842,7 +2842,7 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="65" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B20" s="65"/>
       <c r="C20" s="65"/>
@@ -2850,13 +2850,13 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="35" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D22" s="106"/>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="35" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B23" s="107"/>
     </row>
@@ -2874,7 +2874,7 @@
         <v>23</v>
       </c>
       <c r="B27" s="35">
-        <f>SUM('이름(LCBLxx-xx)'!R1)</f>
+        <f>SUM('이름(LCBxx-xx)'!R1)</f>
         <v>1</v>
       </c>
     </row>
@@ -2883,7 +2883,7 @@
         <v>24</v>
       </c>
       <c r="B28" s="44">
-        <f>SUM('이름(LCBLxx-xx)'!R2)</f>
+        <f>SUM('이름(LCBxx-xx)'!R2)</f>
         <v>0</v>
       </c>
     </row>
@@ -3187,24 +3187,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="162" customHeight="1">
-      <c r="C1" s="126" t="s">
-        <v>131</v>
-      </c>
-      <c r="D1" s="126"/>
-      <c r="E1" s="126"/>
-      <c r="F1" s="126"/>
-      <c r="G1" s="126"/>
-      <c r="H1" s="126"/>
-      <c r="I1" s="126"/>
-      <c r="J1" s="126"/>
-      <c r="K1" s="126"/>
+      <c r="C1" s="137" t="s">
+        <v>141</v>
+      </c>
+      <c r="D1" s="137"/>
+      <c r="E1" s="137"/>
+      <c r="F1" s="137"/>
+      <c r="G1" s="137"/>
+      <c r="H1" s="137"/>
+      <c r="I1" s="137"/>
+      <c r="J1" s="137"/>
+      <c r="K1" s="137"/>
       <c r="L1" s="76" t="s">
         <v>105</v>
       </c>
-      <c r="M1" s="122" t="s">
-        <v>132</v>
-      </c>
-      <c r="N1" s="123"/>
+      <c r="M1" s="133" t="s">
+        <v>142</v>
+      </c>
+      <c r="N1" s="134"/>
       <c r="R1" s="23">
         <f>D11</f>
         <v>1</v>
@@ -3233,22 +3233,22 @@
       <c r="D2" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="124" t="s">
+      <c r="E2" s="135" t="s">
         <v>130</v>
       </c>
-      <c r="F2" s="124"/>
-      <c r="G2" s="125"/>
-      <c r="H2" s="125"/>
-      <c r="I2" s="109" t="s">
+      <c r="F2" s="135"/>
+      <c r="G2" s="136"/>
+      <c r="H2" s="136"/>
+      <c r="I2" s="143" t="s">
         <v>71</v>
       </c>
-      <c r="J2" s="110"/>
-      <c r="K2" s="111"/>
-      <c r="L2" s="118" t="s">
+      <c r="J2" s="144"/>
+      <c r="K2" s="145"/>
+      <c r="L2" s="152" t="s">
         <v>95</v>
       </c>
-      <c r="M2" s="119"/>
-      <c r="N2" s="130"/>
+      <c r="M2" s="153"/>
+      <c r="N2" s="141"/>
       <c r="R2" s="24">
         <f>N16</f>
         <v>0</v>
@@ -3281,12 +3281,12 @@
       <c r="F3" s="108"/>
       <c r="G3" s="108"/>
       <c r="H3" s="108"/>
-      <c r="I3" s="112"/>
-      <c r="J3" s="113"/>
-      <c r="K3" s="114"/>
-      <c r="L3" s="120"/>
-      <c r="M3" s="121"/>
-      <c r="N3" s="131"/>
+      <c r="I3" s="146"/>
+      <c r="J3" s="147"/>
+      <c r="K3" s="148"/>
+      <c r="L3" s="154"/>
+      <c r="M3" s="155"/>
+      <c r="N3" s="142"/>
       <c r="Q3" s="3"/>
       <c r="R3" s="3"/>
       <c r="S3" s="3"/>
@@ -3318,16 +3318,16 @@
       <c r="F4" s="108"/>
       <c r="G4" s="108"/>
       <c r="H4" s="108"/>
-      <c r="I4" s="115" t="s">
+      <c r="I4" s="149" t="s">
         <v>9</v>
       </c>
-      <c r="J4" s="116"/>
-      <c r="K4" s="117"/>
-      <c r="L4" s="127" t="s">
+      <c r="J4" s="150"/>
+      <c r="K4" s="151"/>
+      <c r="L4" s="138" t="s">
         <v>96</v>
       </c>
-      <c r="M4" s="128"/>
-      <c r="N4" s="129"/>
+      <c r="M4" s="139"/>
+      <c r="N4" s="140"/>
       <c r="T4" s="33" t="s">
         <v>1</v>
       </c>
@@ -3388,7 +3388,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="C6" s="58">
         <f>VLOOKUP(MAX(E6,J6),'Row data'!$B$8:$C$19,2,TRUE)</f>
@@ -3534,21 +3534,21 @@
       <c r="N11" s="13"/>
     </row>
     <row r="12" spans="1:23" s="2" customFormat="1" ht="54" customHeight="1">
-      <c r="A12" s="150" t="s">
+      <c r="A12" s="109" t="s">
         <v>86</v>
       </c>
-      <c r="B12" s="150"/>
-      <c r="C12" s="150"/>
-      <c r="D12" s="150"/>
-      <c r="E12" s="150"/>
-      <c r="F12" s="150" t="s">
+      <c r="B12" s="109"/>
+      <c r="C12" s="109"/>
+      <c r="D12" s="109"/>
+      <c r="E12" s="109"/>
+      <c r="F12" s="109" t="s">
         <v>87</v>
       </c>
-      <c r="G12" s="150"/>
-      <c r="H12" s="150"/>
-      <c r="I12" s="150"/>
-      <c r="J12" s="150"/>
-      <c r="K12" s="150"/>
+      <c r="G12" s="109"/>
+      <c r="H12" s="109"/>
+      <c r="I12" s="109"/>
+      <c r="J12" s="109"/>
+      <c r="K12" s="109"/>
       <c r="L12" s="108" t="s">
         <v>15</v>
       </c>
@@ -3560,19 +3560,19 @@
       <c r="P12" s="23"/>
     </row>
     <row r="13" spans="1:23" s="2" customFormat="1" ht="52.9" customHeight="1">
-      <c r="A13" s="151" t="s">
-        <v>143</v>
-      </c>
-      <c r="B13" s="152"/>
-      <c r="C13" s="152"/>
-      <c r="D13" s="152"/>
-      <c r="E13" s="152"/>
-      <c r="F13" s="153"/>
-      <c r="G13" s="153"/>
-      <c r="H13" s="153"/>
-      <c r="I13" s="153"/>
-      <c r="J13" s="153"/>
-      <c r="K13" s="153"/>
+      <c r="A13" s="110" t="s">
+        <v>140</v>
+      </c>
+      <c r="B13" s="111"/>
+      <c r="C13" s="111"/>
+      <c r="D13" s="111"/>
+      <c r="E13" s="111"/>
+      <c r="F13" s="112"/>
+      <c r="G13" s="112"/>
+      <c r="H13" s="112"/>
+      <c r="I13" s="112"/>
+      <c r="J13" s="112"/>
+      <c r="K13" s="112"/>
       <c r="L13" s="80" t="s">
         <v>16</v>
       </c>
@@ -3586,17 +3586,17 @@
       </c>
     </row>
     <row r="14" spans="1:23" s="2" customFormat="1" ht="52.9" customHeight="1">
-      <c r="A14" s="152"/>
-      <c r="B14" s="152"/>
-      <c r="C14" s="152"/>
-      <c r="D14" s="152"/>
-      <c r="E14" s="152"/>
-      <c r="F14" s="153"/>
-      <c r="G14" s="153"/>
-      <c r="H14" s="153"/>
-      <c r="I14" s="153"/>
-      <c r="J14" s="153"/>
-      <c r="K14" s="153"/>
+      <c r="A14" s="111"/>
+      <c r="B14" s="111"/>
+      <c r="C14" s="111"/>
+      <c r="D14" s="111"/>
+      <c r="E14" s="111"/>
+      <c r="F14" s="112"/>
+      <c r="G14" s="112"/>
+      <c r="H14" s="112"/>
+      <c r="I14" s="112"/>
+      <c r="J14" s="112"/>
+      <c r="K14" s="112"/>
       <c r="L14" s="80" t="s">
         <v>106</v>
       </c>
@@ -3610,17 +3610,17 @@
       </c>
     </row>
     <row r="15" spans="1:23" s="2" customFormat="1" ht="52.9" customHeight="1">
-      <c r="A15" s="152"/>
-      <c r="B15" s="152"/>
-      <c r="C15" s="152"/>
-      <c r="D15" s="152"/>
-      <c r="E15" s="152"/>
-      <c r="F15" s="153"/>
-      <c r="G15" s="153"/>
-      <c r="H15" s="153"/>
-      <c r="I15" s="153"/>
-      <c r="J15" s="153"/>
-      <c r="K15" s="153"/>
+      <c r="A15" s="111"/>
+      <c r="B15" s="111"/>
+      <c r="C15" s="111"/>
+      <c r="D15" s="111"/>
+      <c r="E15" s="111"/>
+      <c r="F15" s="112"/>
+      <c r="G15" s="112"/>
+      <c r="H15" s="112"/>
+      <c r="I15" s="112"/>
+      <c r="J15" s="112"/>
+      <c r="K15" s="112"/>
       <c r="L15" s="80" t="s">
         <v>107</v>
       </c>
@@ -3634,18 +3634,18 @@
       </c>
     </row>
     <row r="16" spans="1:23" s="2" customFormat="1" ht="54" customHeight="1">
-      <c r="A16" s="152"/>
-      <c r="B16" s="152"/>
-      <c r="C16" s="152"/>
-      <c r="D16" s="152"/>
-      <c r="E16" s="152"/>
-      <c r="F16" s="153"/>
-      <c r="G16" s="153"/>
-      <c r="H16" s="153"/>
-      <c r="I16" s="153"/>
-      <c r="J16" s="153"/>
-      <c r="K16" s="153"/>
-      <c r="L16" s="154" t="s">
+      <c r="A16" s="111"/>
+      <c r="B16" s="111"/>
+      <c r="C16" s="111"/>
+      <c r="D16" s="111"/>
+      <c r="E16" s="111"/>
+      <c r="F16" s="112"/>
+      <c r="G16" s="112"/>
+      <c r="H16" s="112"/>
+      <c r="I16" s="112"/>
+      <c r="J16" s="112"/>
+      <c r="K16" s="112"/>
+      <c r="L16" s="113" t="s">
         <v>88</v>
       </c>
       <c r="M16" s="77" t="s">
@@ -3657,18 +3657,18 @@
       </c>
     </row>
     <row r="17" spans="1:14" s="2" customFormat="1" ht="46.5" customHeight="1">
-      <c r="A17" s="152"/>
-      <c r="B17" s="152"/>
-      <c r="C17" s="152"/>
-      <c r="D17" s="152"/>
-      <c r="E17" s="152"/>
-      <c r="F17" s="153"/>
-      <c r="G17" s="153"/>
-      <c r="H17" s="153"/>
-      <c r="I17" s="153"/>
-      <c r="J17" s="153"/>
-      <c r="K17" s="153"/>
-      <c r="L17" s="155"/>
+      <c r="A17" s="111"/>
+      <c r="B17" s="111"/>
+      <c r="C17" s="111"/>
+      <c r="D17" s="111"/>
+      <c r="E17" s="111"/>
+      <c r="F17" s="112"/>
+      <c r="G17" s="112"/>
+      <c r="H17" s="112"/>
+      <c r="I17" s="112"/>
+      <c r="J17" s="112"/>
+      <c r="K17" s="112"/>
+      <c r="L17" s="114"/>
       <c r="M17" s="78" t="s">
         <v>18</v>
       </c>
@@ -3678,18 +3678,18 @@
       </c>
     </row>
     <row r="18" spans="1:14" s="2" customFormat="1" ht="46.5" customHeight="1">
-      <c r="A18" s="152"/>
-      <c r="B18" s="152"/>
-      <c r="C18" s="152"/>
-      <c r="D18" s="152"/>
-      <c r="E18" s="152"/>
-      <c r="F18" s="153"/>
-      <c r="G18" s="153"/>
-      <c r="H18" s="153"/>
-      <c r="I18" s="153"/>
-      <c r="J18" s="153"/>
-      <c r="K18" s="153"/>
-      <c r="L18" s="155"/>
+      <c r="A18" s="111"/>
+      <c r="B18" s="111"/>
+      <c r="C18" s="111"/>
+      <c r="D18" s="111"/>
+      <c r="E18" s="111"/>
+      <c r="F18" s="112"/>
+      <c r="G18" s="112"/>
+      <c r="H18" s="112"/>
+      <c r="I18" s="112"/>
+      <c r="J18" s="112"/>
+      <c r="K18" s="112"/>
+      <c r="L18" s="114"/>
       <c r="M18" s="79" t="s">
         <v>19</v>
       </c>
@@ -3699,18 +3699,18 @@
       </c>
     </row>
     <row r="19" spans="1:14" s="2" customFormat="1" ht="52.9" customHeight="1">
-      <c r="A19" s="152"/>
-      <c r="B19" s="152"/>
-      <c r="C19" s="152"/>
-      <c r="D19" s="152"/>
-      <c r="E19" s="152"/>
-      <c r="F19" s="153"/>
-      <c r="G19" s="153"/>
-      <c r="H19" s="153"/>
-      <c r="I19" s="153"/>
-      <c r="J19" s="153"/>
-      <c r="K19" s="153"/>
-      <c r="L19" s="155"/>
+      <c r="A19" s="111"/>
+      <c r="B19" s="111"/>
+      <c r="C19" s="111"/>
+      <c r="D19" s="111"/>
+      <c r="E19" s="111"/>
+      <c r="F19" s="112"/>
+      <c r="G19" s="112"/>
+      <c r="H19" s="112"/>
+      <c r="I19" s="112"/>
+      <c r="J19" s="112"/>
+      <c r="K19" s="112"/>
+      <c r="L19" s="114"/>
       <c r="M19" s="14" t="s">
         <v>20</v>
       </c>
@@ -3736,65 +3736,65 @@
       <c r="N20" s="82"/>
     </row>
     <row r="21" spans="1:14" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="A21" s="133" t="s">
-        <v>142</v>
-      </c>
-      <c r="B21" s="133"/>
-      <c r="C21" s="133"/>
-      <c r="D21" s="133"/>
-      <c r="E21" s="133"/>
-      <c r="F21" s="133"/>
-      <c r="G21" s="133"/>
-      <c r="H21" s="133"/>
-      <c r="I21" s="133"/>
-      <c r="J21" s="133"/>
-      <c r="K21" s="133"/>
-      <c r="L21" s="133"/>
-      <c r="M21" s="133"/>
-      <c r="N21" s="133"/>
+      <c r="A21" s="116" t="s">
+        <v>139</v>
+      </c>
+      <c r="B21" s="116"/>
+      <c r="C21" s="116"/>
+      <c r="D21" s="116"/>
+      <c r="E21" s="116"/>
+      <c r="F21" s="116"/>
+      <c r="G21" s="116"/>
+      <c r="H21" s="116"/>
+      <c r="I21" s="116"/>
+      <c r="J21" s="116"/>
+      <c r="K21" s="116"/>
+      <c r="L21" s="116"/>
+      <c r="M21" s="116"/>
+      <c r="N21" s="116"/>
     </row>
     <row r="22" spans="1:14" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="A22" s="134" t="s">
+      <c r="A22" s="117" t="s">
         <v>89</v>
       </c>
-      <c r="B22" s="134"/>
-      <c r="C22" s="134"/>
-      <c r="D22" s="134"/>
-      <c r="E22" s="134"/>
-      <c r="F22" s="134"/>
-      <c r="G22" s="134"/>
-      <c r="H22" s="134"/>
-      <c r="I22" s="134"/>
-      <c r="J22" s="134"/>
-      <c r="K22" s="134"/>
-      <c r="L22" s="134"/>
-      <c r="M22" s="134"/>
-      <c r="N22" s="134"/>
+      <c r="B22" s="117"/>
+      <c r="C22" s="117"/>
+      <c r="D22" s="117"/>
+      <c r="E22" s="117"/>
+      <c r="F22" s="117"/>
+      <c r="G22" s="117"/>
+      <c r="H22" s="117"/>
+      <c r="I22" s="117"/>
+      <c r="J22" s="117"/>
+      <c r="K22" s="117"/>
+      <c r="L22" s="117"/>
+      <c r="M22" s="117"/>
+      <c r="N22" s="117"/>
     </row>
     <row r="23" spans="1:14" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="A23" s="134"/>
-      <c r="B23" s="134"/>
-      <c r="C23" s="134"/>
-      <c r="D23" s="134"/>
-      <c r="E23" s="134"/>
-      <c r="F23" s="134"/>
-      <c r="G23" s="134"/>
-      <c r="H23" s="134"/>
-      <c r="I23" s="134"/>
-      <c r="J23" s="134"/>
-      <c r="K23" s="134"/>
-      <c r="L23" s="134"/>
-      <c r="M23" s="134"/>
-      <c r="N23" s="134"/>
+      <c r="A23" s="117"/>
+      <c r="B23" s="117"/>
+      <c r="C23" s="117"/>
+      <c r="D23" s="117"/>
+      <c r="E23" s="117"/>
+      <c r="F23" s="117"/>
+      <c r="G23" s="117"/>
+      <c r="H23" s="117"/>
+      <c r="I23" s="117"/>
+      <c r="J23" s="117"/>
+      <c r="K23" s="117"/>
+      <c r="L23" s="117"/>
+      <c r="M23" s="117"/>
+      <c r="N23" s="117"/>
     </row>
     <row r="24" spans="1:14" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="A24" s="135" t="s">
+      <c r="A24" s="118" t="s">
         <v>21</v>
       </c>
-      <c r="B24" s="136"/>
-      <c r="C24" s="141"/>
-      <c r="D24" s="142"/>
-      <c r="E24" s="143"/>
+      <c r="B24" s="119"/>
+      <c r="C24" s="124"/>
+      <c r="D24" s="125"/>
+      <c r="E24" s="126"/>
       <c r="F24" s="26"/>
       <c r="G24" s="15"/>
       <c r="H24" s="15"/>
@@ -3803,73 +3803,73 @@
       <c r="K24" s="108" t="s">
         <v>22</v>
       </c>
-      <c r="L24" s="132"/>
-      <c r="M24" s="132"/>
-      <c r="N24" s="132"/>
+      <c r="L24" s="115"/>
+      <c r="M24" s="115"/>
+      <c r="N24" s="115"/>
     </row>
     <row r="25" spans="1:14" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="A25" s="137"/>
-      <c r="B25" s="138"/>
-      <c r="C25" s="144"/>
-      <c r="D25" s="145"/>
-      <c r="E25" s="146"/>
+      <c r="A25" s="120"/>
+      <c r="B25" s="121"/>
+      <c r="C25" s="127"/>
+      <c r="D25" s="128"/>
+      <c r="E25" s="129"/>
       <c r="F25" s="26"/>
       <c r="G25" s="26"/>
       <c r="H25" s="26"/>
       <c r="I25" s="15"/>
       <c r="J25" s="15"/>
       <c r="K25" s="108"/>
-      <c r="L25" s="132"/>
-      <c r="M25" s="132"/>
-      <c r="N25" s="132"/>
+      <c r="L25" s="115"/>
+      <c r="M25" s="115"/>
+      <c r="N25" s="115"/>
     </row>
     <row r="26" spans="1:14" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="A26" s="137"/>
-      <c r="B26" s="138"/>
-      <c r="C26" s="144"/>
-      <c r="D26" s="145"/>
-      <c r="E26" s="146"/>
+      <c r="A26" s="120"/>
+      <c r="B26" s="121"/>
+      <c r="C26" s="127"/>
+      <c r="D26" s="128"/>
+      <c r="E26" s="129"/>
       <c r="F26" s="26"/>
       <c r="G26" s="26"/>
       <c r="H26" s="26"/>
       <c r="I26" s="15"/>
       <c r="J26" s="15"/>
       <c r="K26" s="108"/>
-      <c r="L26" s="132"/>
-      <c r="M26" s="132"/>
-      <c r="N26" s="132"/>
+      <c r="L26" s="115"/>
+      <c r="M26" s="115"/>
+      <c r="N26" s="115"/>
     </row>
     <row r="27" spans="1:14" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="A27" s="137"/>
-      <c r="B27" s="138"/>
-      <c r="C27" s="144"/>
-      <c r="D27" s="145"/>
-      <c r="E27" s="146"/>
+      <c r="A27" s="120"/>
+      <c r="B27" s="121"/>
+      <c r="C27" s="127"/>
+      <c r="D27" s="128"/>
+      <c r="E27" s="129"/>
       <c r="F27" s="26"/>
       <c r="G27" s="26"/>
       <c r="H27" s="26"/>
       <c r="I27" s="15"/>
       <c r="J27" s="15"/>
       <c r="K27" s="108"/>
-      <c r="L27" s="132"/>
-      <c r="M27" s="132"/>
-      <c r="N27" s="132"/>
+      <c r="L27" s="115"/>
+      <c r="M27" s="115"/>
+      <c r="N27" s="115"/>
     </row>
     <row r="28" spans="1:14" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="A28" s="139"/>
-      <c r="B28" s="140"/>
-      <c r="C28" s="147"/>
-      <c r="D28" s="148"/>
-      <c r="E28" s="149"/>
+      <c r="A28" s="122"/>
+      <c r="B28" s="123"/>
+      <c r="C28" s="130"/>
+      <c r="D28" s="131"/>
+      <c r="E28" s="132"/>
       <c r="F28" s="26"/>
       <c r="G28" s="26"/>
       <c r="H28" s="26"/>
       <c r="I28" s="15"/>
       <c r="J28" s="15"/>
       <c r="K28" s="108"/>
-      <c r="L28" s="132"/>
-      <c r="M28" s="132"/>
-      <c r="N28" s="132"/>
+      <c r="L28" s="115"/>
+      <c r="M28" s="115"/>
+      <c r="N28" s="115"/>
     </row>
     <row r="29" spans="1:14" s="2" customFormat="1" ht="31.5">
       <c r="A29" s="3"/>
@@ -3958,12 +3958,19 @@
     <row r="62" ht="23.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="A12:E12"/>
-    <mergeCell ref="A13:E19"/>
-    <mergeCell ref="F12:K12"/>
-    <mergeCell ref="F13:K19"/>
-    <mergeCell ref="L16:L19"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="I2:K3"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="L2:M3"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:H2"/>
+    <mergeCell ref="C1:K1"/>
+    <mergeCell ref="L4:N4"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="B4:H4"/>
     <mergeCell ref="K24:K28"/>
     <mergeCell ref="L24:N28"/>
     <mergeCell ref="A21:N21"/>
@@ -3971,19 +3978,12 @@
     <mergeCell ref="A24:B28"/>
     <mergeCell ref="C24:E28"/>
     <mergeCell ref="A23:N23"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:H2"/>
-    <mergeCell ref="C1:K1"/>
-    <mergeCell ref="L4:N4"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="I2:K3"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="L2:M3"/>
-    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A13:E19"/>
+    <mergeCell ref="F12:K12"/>
+    <mergeCell ref="F13:K19"/>
+    <mergeCell ref="L16:L19"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="L6">
